--- a/Data/待床日与住院天数.xlsx
+++ b/Data/待床日与住院天数.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>年月</t>
   </si>
@@ -32,6 +32,9 @@
     <t>平均住院天数</t>
   </si>
   <si>
+    <t>2023-12</t>
+  </si>
+  <si>
     <t>2024-01</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
     <t>2024-11</t>
   </si>
   <si>
+    <t>2024-12</t>
+  </si>
+  <si>
     <t>待床日</t>
   </si>
   <si>
@@ -74,25 +80,22 @@
     <t>核算年月</t>
   </si>
   <si>
-    <t>2024-12</t>
-  </si>
-  <si>
     <t>index</t>
   </si>
   <si>
-    <t>总数</t>
-  </si>
-  <si>
-    <t>个数</t>
-  </si>
-  <si>
-    <t>平均数</t>
-  </si>
-  <si>
-    <t>众数</t>
-  </si>
-  <si>
-    <t>中位数</t>
+    <t>待床日总天数</t>
+  </si>
+  <si>
+    <t>住院人数</t>
+  </si>
+  <si>
+    <t>平均天数</t>
+  </si>
+  <si>
+    <t>众数天数</t>
+  </si>
+  <si>
+    <t>中位数天数</t>
   </si>
   <si>
     <t>日间手术待床日</t>
@@ -105,6 +108,12 @@
   </si>
   <si>
     <t>预住院住院日</t>
+  </si>
+  <si>
+    <t>总计待床日</t>
+  </si>
+  <si>
+    <t>总计住院日</t>
   </si>
 </sst>
 </file>
@@ -462,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -512,13 +521,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1.195121951219512</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -526,13 +535,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C5">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>1.105263157894737</v>
+        <v>1.195121951219512</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -540,13 +549,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C6">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D6">
-        <v>1.132530120481928</v>
+        <v>1.105263157894737</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -554,13 +563,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7">
-        <v>1.081395348837209</v>
+        <v>1.132530120481928</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -568,13 +577,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C8">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D8">
-        <v>1.085714285714286</v>
+        <v>1.081395348837209</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -582,13 +591,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C9">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9">
-        <v>1.131313131313131</v>
+        <v>1.085714285714286</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -596,13 +605,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C10">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10">
-        <v>1.095238095238095</v>
+        <v>1.131313131313131</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -610,13 +619,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C11">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D11">
-        <v>1.094736842105263</v>
+        <v>1.095238095238095</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -624,13 +633,41 @@
         <v>14</v>
       </c>
       <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>104</v>
+      </c>
+      <c r="D12">
+        <v>1.094736842105263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>125</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>141</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>1.128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>90</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>1.111111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -640,7 +677,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -651,13 +688,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -668,19 +705,19 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1.166666666666667</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>3.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -688,19 +725,19 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>258</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>592</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>3.146341463414634</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="F3">
-        <v>7.219512195121951</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -708,19 +745,19 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="C4">
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="D4">
-        <v>1051</v>
+        <v>592</v>
       </c>
       <c r="E4">
-        <v>2.034090909090909</v>
+        <v>3.146341463414634</v>
       </c>
       <c r="F4">
-        <v>5.971590909090909</v>
+        <v>7.219512195121951</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -728,19 +765,19 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="C5">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="D5">
-        <v>540</v>
+        <v>1051</v>
       </c>
       <c r="E5">
-        <v>1.234042553191489</v>
+        <v>2.034090909090909</v>
       </c>
       <c r="F5">
-        <v>3.829787234042553</v>
+        <v>5.971590909090909</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -748,19 +785,19 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C6">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="D6">
-        <v>613</v>
+        <v>540</v>
       </c>
       <c r="E6">
-        <v>1.426751592356688</v>
+        <v>1.234042553191489</v>
       </c>
       <c r="F6">
-        <v>3.904458598726114</v>
+        <v>3.829787234042553</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -768,19 +805,19 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="D7">
-        <v>238</v>
+        <v>613</v>
       </c>
       <c r="E7">
-        <v>0.7889908256880734</v>
+        <v>1.426751592356688</v>
       </c>
       <c r="F7">
-        <v>2.18348623853211</v>
+        <v>3.904458598726114</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -788,19 +825,19 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="C8">
-        <v>246</v>
+        <v>86</v>
       </c>
       <c r="D8">
-        <v>698</v>
+        <v>238</v>
       </c>
       <c r="E8">
-        <v>1.366666666666667</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="F8">
-        <v>3.877777777777778</v>
+        <v>2.18348623853211</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -808,19 +845,19 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C9">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D9">
-        <v>621</v>
+        <v>698</v>
       </c>
       <c r="E9">
-        <v>1.484662576687117</v>
+        <v>1.366666666666667</v>
       </c>
       <c r="F9">
-        <v>3.809815950920246</v>
+        <v>3.877777777777778</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -828,19 +865,19 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C10">
-        <v>118</v>
+        <v>242</v>
       </c>
       <c r="D10">
-        <v>298</v>
+        <v>621</v>
       </c>
       <c r="E10">
-        <v>0.8613138686131386</v>
+        <v>1.484662576687117</v>
       </c>
       <c r="F10">
-        <v>2.175182481751825</v>
+        <v>3.809815950920246</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -848,19 +885,19 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C11">
-        <v>400</v>
+        <v>118</v>
       </c>
       <c r="D11">
-        <v>913</v>
+        <v>298</v>
       </c>
       <c r="E11">
-        <v>1.990049751243781</v>
+        <v>0.8613138686131386</v>
       </c>
       <c r="F11">
-        <v>4.54228855721393</v>
+        <v>2.175182481751825</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -868,19 +905,59 @@
         <v>14</v>
       </c>
       <c r="B12">
+        <v>201</v>
+      </c>
+      <c r="C12">
+        <v>400</v>
+      </c>
+      <c r="D12">
+        <v>913</v>
+      </c>
+      <c r="E12">
+        <v>1.990049751243781</v>
+      </c>
+      <c r="F12">
+        <v>4.54228855721393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>258</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>452</v>
       </c>
-      <c r="D12">
-        <v>1113</v>
-      </c>
-      <c r="E12">
+      <c r="D13">
+        <v>1114</v>
+      </c>
+      <c r="E13">
         <v>1.751937984496124</v>
       </c>
-      <c r="F12">
-        <v>4.313953488372093</v>
+      <c r="F13">
+        <v>4.317829457364341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>151</v>
+      </c>
+      <c r="C14">
+        <v>221</v>
+      </c>
+      <c r="D14">
+        <v>484</v>
+      </c>
+      <c r="E14">
+        <v>1.463576158940397</v>
+      </c>
+      <c r="F14">
+        <v>3.205298013245033</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +972,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -909,13 +986,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -923,7 +1000,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>31</v>
@@ -937,7 +1014,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>75</v>
@@ -951,7 +1028,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>77</v>
@@ -965,7 +1042,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>93</v>
@@ -979,7 +1056,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>101</v>
@@ -993,7 +1070,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -1007,7 +1084,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>107</v>
@@ -1021,7 +1098,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -1035,7 +1112,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>128</v>
@@ -1049,16 +1126,16 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="D12">
-        <v>1.055555555555556</v>
+        <v>1.101851851851852</v>
       </c>
     </row>
   </sheetData>
@@ -1073,19 +1150,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1093,27 +1170,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="F2">
-        <v>4.2</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>51</v>
@@ -1133,7 +1210,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>188</v>
@@ -1153,7 +1230,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>142</v>
@@ -1173,7 +1250,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>145</v>
@@ -1193,7 +1270,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>126</v>
@@ -1213,7 +1290,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>165</v>
@@ -1233,7 +1310,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>155</v>
@@ -1253,7 +1330,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>145</v>
@@ -1273,7 +1350,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>176</v>
@@ -1293,7 +1370,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>280</v>
@@ -1313,22 +1390,22 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C13">
-        <v>64</v>
+        <v>285</v>
       </c>
       <c r="D13">
-        <v>115</v>
+        <v>600</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1.557377049180328</v>
       </c>
       <c r="F13">
-        <v>3.59375</v>
+        <v>3.278688524590164</v>
       </c>
     </row>
   </sheetData>
@@ -1338,41 +1415,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
-        <v>478</v>
+        <v>523</v>
       </c>
       <c r="C2">
-        <v>824</v>
+        <v>914</v>
       </c>
       <c r="D2">
-        <v>0.5800970873786407</v>
+        <v>0.5722100656455142</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1383,16 +1460,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
-        <v>2080</v>
+        <v>2264</v>
       </c>
       <c r="C3">
-        <v>778</v>
+        <v>848</v>
       </c>
       <c r="D3">
-        <v>2.673521850899743</v>
+        <v>2.669811320754717</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1403,16 +1480,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>906</v>
+        <v>1003</v>
       </c>
       <c r="C4">
-        <v>824</v>
+        <v>914</v>
       </c>
       <c r="D4">
-        <v>1.099514563106796</v>
+        <v>1.097374179431072</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1423,22 +1500,62 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>5728</v>
+        <v>6182</v>
       </c>
       <c r="C5">
-        <v>778</v>
+        <v>848</v>
       </c>
       <c r="D5">
-        <v>7.362467866323907</v>
+        <v>7.290094339622642</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
       <c r="F5">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>2787</v>
+      </c>
+      <c r="C6">
+        <v>1762</v>
+      </c>
+      <c r="D6">
+        <v>1.581725312145289</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>7185</v>
+      </c>
+      <c r="C7">
+        <v>1762</v>
+      </c>
+      <c r="D7">
+        <v>4.077752553916005</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
